--- a/erp-server/erp-server-tms/src/main/resources/excel/firstMileWeightChangeTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/firstMileWeightChangeTemplate.xlsx
@@ -41,6 +41,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Courier New"/>
+        <charset val="134"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -54,6 +60,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Courier New"/>
+        <charset val="134"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -75,6 +87,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Courier New"/>
+        <charset val="134"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -100,13 +118,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="6">
+  <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0_ "/>
-    <numFmt numFmtId="177" formatCode="0.000000_ "/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -279,12 +295,12 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Courier New"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -738,23 +754,20 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1071,43 +1084,44 @@
   <dimension ref="A1:I1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="15.875" customWidth="1"/>
-    <col min="2" max="2" width="20.25" customWidth="1"/>
+    <col min="1" max="1" width="15.875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.25" style="2" customWidth="1"/>
     <col min="3" max="3" width="17.5" style="2" customWidth="1"/>
-    <col min="4" max="4" width="18.375" customWidth="1"/>
-    <col min="5" max="5" width="20.375" style="3" customWidth="1"/>
-    <col min="6" max="6" width="17.75" customWidth="1"/>
-    <col min="7" max="7" width="16.875" customWidth="1"/>
-    <col min="8" max="8" width="12.625" customWidth="1"/>
-    <col min="9" max="9" width="14.25" customWidth="1"/>
+    <col min="4" max="4" width="18.375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="20.375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="17.75" style="2" customWidth="1"/>
+    <col min="7" max="7" width="16.875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="12.625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="14.25" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:9">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/erp-server/erp-server-tms/src/main/resources/excel/firstMileWeightChangeTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/firstMileWeightChangeTemplate.xlsx
@@ -41,17 +41,11 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Courier New"/>
-        <charset val="134"/>
-      </rPr>
       <t>*</t>
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
+        <sz val="11"/>
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
@@ -60,17 +54,11 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Courier New"/>
-        <charset val="134"/>
-      </rPr>
       <t>*</t>
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
+        <sz val="11"/>
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
@@ -78,7 +66,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
+        <sz val="11"/>
         <rFont val="Courier New"/>
         <charset val="134"/>
       </rPr>
@@ -87,17 +75,11 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Courier New"/>
-        <charset val="134"/>
-      </rPr>
       <t>*</t>
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
+        <sz val="11"/>
         <rFont val="Courier New"/>
         <charset val="134"/>
       </rPr>
@@ -124,7 +106,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -139,12 +121,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9.8"/>
+      <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Courier New"/>
       <charset val="134"/>
@@ -294,12 +276,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
+      <sz val="11"/>
       <name val="Courier New"/>
       <charset val="134"/>
     </font>
@@ -1096,7 +1073,7 @@
     <col min="10" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:9">
+    <row r="1" s="1" customFormat="1" ht="15" spans="1:9">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>

--- a/erp-server/erp-server-tms/src/main/resources/excel/firstMileWeightChangeTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/firstMileWeightChangeTemplate.xlsx
@@ -41,6 +41,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Courier New"/>
+        <charset val="134"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -54,6 +60,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Courier New"/>
+        <charset val="134"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -75,6 +87,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Courier New"/>
+        <charset val="134"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -100,11 +118,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -731,7 +750,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -741,7 +760,13 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
@@ -1064,7 +1089,7 @@
     <col min="1" max="1" width="15.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="20.25" style="2" customWidth="1"/>
     <col min="3" max="3" width="17.5" style="2" customWidth="1"/>
-    <col min="4" max="4" width="18.375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="18.375" style="3" customWidth="1"/>
     <col min="5" max="5" width="20.375" style="2" customWidth="1"/>
     <col min="6" max="6" width="17.75" style="2" customWidth="1"/>
     <col min="7" max="7" width="16.875" style="2" customWidth="1"/>
@@ -1074,31 +1099,31 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="15" spans="1:9">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
     </row>
